--- a/data/trans_camb/IP16A01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-56,15; -24,63</t>
+          <t>-56,72; -23,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-62,09; -20,76</t>
+          <t>-61,83; -20,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-93,13; -33,73</t>
+          <t>-94,11; -34,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-58,16; -20,93</t>
+          <t>-58,6; -20,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-61,28; -7,2</t>
+          <t>-58,05; -7,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,97; -22,59</t>
+          <t>-66,86; -22,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,93; -25,63</t>
+          <t>-52,03; -26,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-52,39; -20,77</t>
+          <t>-51,83; -19,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-77,63; -36,62</t>
+          <t>-76,97; -35,79</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,15; -24,63</t>
+          <t>-56,72; -23,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,09; -20,76</t>
+          <t>-61,83; -20,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-93,13; -33,73</t>
+          <t>-94,11; -34,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,16; -20,93</t>
+          <t>-58,6; -20,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,28; -7,2</t>
+          <t>-58,05; -7,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,97; -22,59</t>
+          <t>-66,86; -22,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,93; -25,63</t>
+          <t>-52,03; -26,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,39; -20,77</t>
+          <t>-51,83; -19,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-77,63; -36,62</t>
+          <t>-76,97; -35,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -24,47</t>
+          <t>-39,86; -24,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -30,91</t>
+          <t>-48,1; -30,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-53,18; -18,85</t>
+          <t>-52,69; -17,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-48,16; -31,11</t>
+          <t>-47,28; -31,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,61; -35,69</t>
+          <t>-52,72; -35,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,86; -31,57</t>
+          <t>-49,67; -32,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -29,82</t>
+          <t>-42,17; -30,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,8; -35,1</t>
+          <t>-48,57; -36,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-46,73; -26,06</t>
+          <t>-47,0; -27,28</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -24,47</t>
+          <t>-39,86; -24,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -30,91</t>
+          <t>-48,1; -30,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,18; -18,85</t>
+          <t>-52,69; -17,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,16; -31,11</t>
+          <t>-47,28; -31,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,61; -35,69</t>
+          <t>-52,72; -35,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,86; -31,57</t>
+          <t>-49,67; -32,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -29,82</t>
+          <t>-42,17; -30,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,8; -35,1</t>
+          <t>-48,57; -36,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,73; -26,06</t>
+          <t>-47,0; -27,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -19,73</t>
+          <t>-44,24; -19,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-51,35; -21,88</t>
+          <t>-51,41; -23,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-54,41; -28,76</t>
+          <t>-52,93; -28,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -21,95</t>
+          <t>-47,51; -22,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,11; -37,07</t>
+          <t>-66,85; -35,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,98; -28,42</t>
+          <t>-55,78; -28,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,49; -23,42</t>
+          <t>-41,23; -24,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,86; -33,47</t>
+          <t>-54,43; -33,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-50,52; -32,02</t>
+          <t>-51,49; -32,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -19,73</t>
+          <t>-44,24; -19,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,35; -21,88</t>
+          <t>-51,41; -23,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,41; -28,76</t>
+          <t>-52,93; -28,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -21,95</t>
+          <t>-47,51; -22,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,11; -37,07</t>
+          <t>-66,85; -35,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,98; -28,42</t>
+          <t>-55,78; -28,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,49; -23,42</t>
+          <t>-41,23; -24,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,86; -33,47</t>
+          <t>-54,43; -33,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,52; -32,02</t>
+          <t>-51,49; -32,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -26,63</t>
+          <t>-39,58; -27,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -32,0</t>
+          <t>-45,72; -31,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -23,97</t>
+          <t>-52,04; -25,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -31,68</t>
+          <t>-43,61; -31,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -37,17</t>
+          <t>-52,05; -37,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -33,48</t>
+          <t>-48,01; -34,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -30,87</t>
+          <t>-39,75; -30,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -36,87</t>
+          <t>-46,5; -36,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -31,58</t>
+          <t>-47,48; -32,13</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,3; -26,63</t>
+          <t>-39,58; -27,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,55; -32,0</t>
+          <t>-45,72; -31,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,3; -23,97</t>
+          <t>-52,04; -25,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,12; -31,68</t>
+          <t>-43,61; -31,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,45; -37,17</t>
+          <t>-52,05; -37,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -33,48</t>
+          <t>-48,01; -34,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -30,87</t>
+          <t>-39,75; -30,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -36,87</t>
+          <t>-46,5; -36,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-47,14; -31,58</t>
+          <t>-47,48; -32,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-56,72; -23,35</t>
+          <t>-55,87; -24,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-61,83; -20,97</t>
+          <t>-62,55; -20,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-94,11; -34,84</t>
+          <t>-92,17; -33,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-58,6; -20,27</t>
+          <t>-58,13; -20,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,05; -7,17</t>
+          <t>-59,07; -7,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,86; -22,48</t>
+          <t>-67,19; -20,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,03; -26,32</t>
+          <t>-50,81; -27,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,83; -19,72</t>
+          <t>-51,48; -20,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-76,97; -35,79</t>
+          <t>-78,02; -36,63</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,72; -23,35</t>
+          <t>-55,87; -24,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,83; -20,97</t>
+          <t>-62,55; -20,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-94,11; -34,84</t>
+          <t>-92,17; -33,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,6; -20,27</t>
+          <t>-58,13; -20,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,05; -7,17</t>
+          <t>-59,07; -7,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,86; -22,48</t>
+          <t>-67,19; -20,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,03; -26,32</t>
+          <t>-50,81; -27,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,83; -19,72</t>
+          <t>-51,48; -20,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,97; -35,79</t>
+          <t>-78,02; -36,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,86; -24,36</t>
+          <t>-40,08; -24,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-48,1; -30,08</t>
+          <t>-48,17; -31,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-52,69; -17,22</t>
+          <t>-52,96; -19,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-47,28; -31,26</t>
+          <t>-47,6; -31,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,72; -35,98</t>
+          <t>-53,25; -35,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,67; -32,6</t>
+          <t>-49,85; -32,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,17; -30,1</t>
+          <t>-42,43; -31,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,57; -36,36</t>
+          <t>-47,59; -36,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -27,28</t>
+          <t>-47,25; -25,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,86; -24,36</t>
+          <t>-40,08; -24,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,1; -30,08</t>
+          <t>-48,17; -31,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,69; -17,22</t>
+          <t>-52,96; -19,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,28; -31,26</t>
+          <t>-47,6; -31,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,72; -35,98</t>
+          <t>-53,25; -35,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,67; -32,6</t>
+          <t>-49,85; -32,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,17; -30,1</t>
+          <t>-42,43; -31,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,57; -36,36</t>
+          <t>-47,59; -36,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -27,28</t>
+          <t>-47,25; -25,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-44,24; -19,01</t>
+          <t>-44,61; -20,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-51,41; -23,38</t>
+          <t>-53,13; -22,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-52,93; -28,97</t>
+          <t>-53,35; -29,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-47,51; -22,72</t>
+          <t>-45,22; -20,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,85; -35,27</t>
+          <t>-66,3; -35,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,78; -28,61</t>
+          <t>-54,14; -28,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-41,23; -24,12</t>
+          <t>-42,46; -24,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,43; -33,14</t>
+          <t>-56,06; -33,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-51,49; -32,53</t>
+          <t>-50,85; -31,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,24; -19,01</t>
+          <t>-44,61; -20,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,41; -23,38</t>
+          <t>-53,13; -22,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,93; -28,97</t>
+          <t>-53,35; -29,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,51; -22,72</t>
+          <t>-45,22; -20,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,85; -35,27</t>
+          <t>-66,3; -35,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,78; -28,61</t>
+          <t>-54,14; -28,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,23; -24,12</t>
+          <t>-42,46; -24,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,43; -33,14</t>
+          <t>-56,06; -33,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,49; -32,53</t>
+          <t>-50,85; -31,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -27,1</t>
+          <t>-38,83; -26,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -31,55</t>
+          <t>-46,26; -31,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,12</t>
+          <t>-51,72; -25,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -31,13</t>
+          <t>-43,93; -30,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -37,33</t>
+          <t>-52,22; -37,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,16</t>
+          <t>-47,82; -34,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -30,8</t>
+          <t>-40,34; -30,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-46,5; -36,81</t>
+          <t>-47,15; -37,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -32,13</t>
+          <t>-46,8; -32,27</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,58; -27,1</t>
+          <t>-38,83; -26,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,72; -31,55</t>
+          <t>-46,26; -31,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,12</t>
+          <t>-51,72; -25,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -31,13</t>
+          <t>-43,93; -30,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -37,33</t>
+          <t>-52,22; -37,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -34,16</t>
+          <t>-47,82; -34,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -30,8</t>
+          <t>-40,34; -30,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,5; -36,81</t>
+          <t>-47,15; -37,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -32,13</t>
+          <t>-46,8; -32,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-37,55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-26,72</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-41,37</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-38,88</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-40,06</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-65,42</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-37,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-26,72</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-44,62</t>
+          <t>-46,52</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-54,88</t>
+          <t>-43,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-55,87; -24,12</t>
+          <t>-58,16; -20,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-62,55; -20,52</t>
+          <t>-61,28; -7,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-92,17; -33,76</t>
+          <t>-65,47; -20,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-58,13; -20,24</t>
+          <t>-56,15; -24,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-59,07; -7,58</t>
+          <t>-62,09; -20,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,19; -20,37</t>
+          <t>-72,33; -24,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,81; -27,49</t>
+          <t>-51,93; -25,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,48; -20,94</t>
+          <t>-52,39; -20,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-78,02; -36,63</t>
+          <t>-60,85; -27,95</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-37,55%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-26,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-41,37%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-38,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-40,06%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-65,42%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-37,55%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-26,72%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-44,62%</t>
+          <t>-46,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-54,88%</t>
+          <t>-43,49%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,87; -24,12</t>
+          <t>-58,16; -20,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,55; -20,52</t>
+          <t>-61,28; -7,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-92,17; -33,76</t>
+          <t>-65,47; -20,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,13; -20,24</t>
+          <t>-56,15; -24,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,07; -7,58</t>
+          <t>-62,09; -20,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,19; -20,37</t>
+          <t>-72,33; -24,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,81; -27,49</t>
+          <t>-51,93; -25,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,48; -20,94</t>
+          <t>-52,39; -20,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-78,02; -36,63</t>
+          <t>-60,85; -27,95</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-39,42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-44,46</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-39,85</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-31,8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-39,16</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-38,63</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-39,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-44,46</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-40,42</t>
+          <t>-47,83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-39,53</t>
+          <t>-43,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-40,08; -24,26</t>
+          <t>-48,16; -31,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-48,17; -31,27</t>
+          <t>-53,61; -35,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-52,96; -19,1</t>
+          <t>-49,74; -30,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-47,6; -31,18</t>
+          <t>-40,79; -24,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,25; -35,55</t>
+          <t>-48,25; -30,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,85; -32,71</t>
+          <t>-56,79; -38,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,43; -31,04</t>
+          <t>-41,82; -29,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,59; -36,14</t>
+          <t>-47,8; -35,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-47,25; -25,3</t>
+          <t>-50,07; -37,92</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-39,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-44,46%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-39,85%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-31,8%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-39,16%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-38,63%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-39,42%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-44,46%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-40,42%</t>
+          <t>-47,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-39,53%</t>
+          <t>-43,54%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,08; -24,26</t>
+          <t>-48,16; -31,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,17; -31,27</t>
+          <t>-53,61; -35,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,96; -19,1</t>
+          <t>-49,74; -30,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,6; -31,18</t>
+          <t>-40,79; -24,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,25; -35,55</t>
+          <t>-48,25; -30,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,85; -32,71</t>
+          <t>-56,79; -38,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,43; -31,04</t>
+          <t>-41,82; -29,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,59; -36,14</t>
+          <t>-47,8; -35,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,25; -25,3</t>
+          <t>-50,07; -37,92</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-32,96</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-51,54</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-41,81</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-31,24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-36,36</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-40,94</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-32,96</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-51,54</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-41,14</t>
+          <t>-39,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-41,04</t>
+          <t>-40,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-44,61; -20,22</t>
+          <t>-46,8; -21,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-53,13; -22,61</t>
+          <t>-68,11; -37,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-53,35; -29,86</t>
+          <t>-57,42; -28,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-45,22; -20,5</t>
+          <t>-47,14; -19,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-66,3; -35,87</t>
+          <t>-51,35; -21,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -28,2</t>
+          <t>-53,58; -27,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,46; -24,19</t>
+          <t>-40,49; -23,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -33,88</t>
+          <t>-54,86; -33,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-50,85; -31,64</t>
+          <t>-50,01; -31,87</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-32,96%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-51,54%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-41,81%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-31,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-36,36%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-40,94%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-32,96%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-51,54%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,14%</t>
+          <t>-39,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-41,04%</t>
+          <t>-40,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,61; -20,22</t>
+          <t>-46,8; -21,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,13; -22,61</t>
+          <t>-68,11; -37,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,35; -29,86</t>
+          <t>-57,42; -28,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,22; -20,5</t>
+          <t>-47,14; -19,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,3; -35,87</t>
+          <t>-51,35; -21,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -28,2</t>
+          <t>-53,58; -27,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,46; -24,19</t>
+          <t>-40,49; -23,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,06; -33,88</t>
+          <t>-54,86; -33,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,85; -31,64</t>
+          <t>-50,01; -31,87</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-37,6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-44,86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-40,49</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-32,77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-38,64</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-41,47</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-37,6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-44,86</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-40,97</t>
+          <t>-45,47</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-41,21</t>
+          <t>-42,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -26,1</t>
+          <t>-44,12; -31,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -31,83</t>
+          <t>-52,45; -37,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -25,75</t>
+          <t>-46,67; -33,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -30,9</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -37,65</t>
+          <t>-46,55; -32,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -34,11</t>
+          <t>-52,8; -38,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -30,98</t>
+          <t>-39,59; -30,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -37,11</t>
+          <t>-46,92; -36,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -32,27</t>
+          <t>-47,6; -38,07</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-37,6%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-44,86%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-40,49%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-32,77%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-38,64%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-41,47%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-37,6%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-44,86%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-40,97%</t>
+          <t>-45,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-41,21%</t>
+          <t>-42,8%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -26,1</t>
+          <t>-44,12; -31,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,26; -31,83</t>
+          <t>-52,45; -37,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,72; -25,75</t>
+          <t>-46,67; -33,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,93; -30,9</t>
+          <t>-39,3; -26,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,22; -37,65</t>
+          <t>-46,55; -32,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -34,11</t>
+          <t>-52,8; -38,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,34; -30,98</t>
+          <t>-39,59; -30,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,15; -37,11</t>
+          <t>-46,92; -36,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -32,27</t>
+          <t>-47,6; -38,07</t>
         </is>
       </c>
     </row>
